--- a/Java_Deprecation_Report.xlsx
+++ b/Java_Deprecation_Report.xlsx
@@ -608,7 +608,7 @@
     <t>MyPojoRequest</t>
   </si>
   <si>
-    <t>deprecatedRequestProperty</t>
+    <t>formerMandatoryRequestProperty</t>
   </si>
 </sst>
 </file>

--- a/Java_Deprecation_Report.xlsx
+++ b/Java_Deprecation_Report.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="192">
   <si>
     <t>Type</t>
   </si>
@@ -603,6 +603,12 @@
   </si>
   <si>
     <t>deprecatedProperty</t>
+  </si>
+  <si>
+    <t>7.0</t>
+  </si>
+  <si>
+    <t>2026-09-13</t>
   </si>
   <si>
     <t>MyPojoRequest</t>
@@ -3772,36 +3778,36 @@
         <v>11</v>
       </c>
       <c r="G102" t="s" s="11">
-        <v>11</v>
+        <v>188</v>
       </c>
       <c r="H102" t="s" s="11">
-        <v>11</v>
+        <v>189</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="9">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B103" t="s" s="9">
         <v>186</v>
       </c>
       <c r="C103" t="s" s="9">
+        <v>191</v>
+      </c>
+      <c r="D103" t="s" s="9">
+        <v>11</v>
+      </c>
+      <c r="E103" t="s" s="9">
+        <v>11</v>
+      </c>
+      <c r="F103" t="s" s="10">
+        <v>11</v>
+      </c>
+      <c r="G103" t="s" s="11">
+        <v>188</v>
+      </c>
+      <c r="H103" t="s" s="11">
         <v>189</v>
-      </c>
-      <c r="D103" t="s" s="9">
-        <v>11</v>
-      </c>
-      <c r="E103" t="s" s="9">
-        <v>11</v>
-      </c>
-      <c r="F103" t="s" s="10">
-        <v>11</v>
-      </c>
-      <c r="G103" t="s" s="11">
-        <v>11</v>
-      </c>
-      <c r="H103" t="s" s="11">
-        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/Java_Deprecation_Report.xlsx
+++ b/Java_Deprecation_Report.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="193">
   <si>
     <t>Type</t>
   </si>
@@ -615,6 +615,9 @@
   </si>
   <si>
     <t>formerMandatoryRequestProperty</t>
+  </si>
+  <si>
+    <t>MyContext</t>
   </si>
 </sst>
 </file>
@@ -1121,7 +1124,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E1136C3-A1B3-DD42-A00A-DCFCD8D149EA}">
-  <dimension ref="A1:H103"/>
+  <dimension ref="A1:H104"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="9" width="31.5"/>
@@ -3810,6 +3813,32 @@
         <v>189</v>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" t="s" s="9">
+        <v>192</v>
+      </c>
+      <c r="B104" t="s" s="9">
+        <v>186</v>
+      </c>
+      <c r="C104" t="s" s="9">
+        <v>63</v>
+      </c>
+      <c r="D104" t="s" s="9">
+        <v>63</v>
+      </c>
+      <c r="E104" t="s" s="9">
+        <v>11</v>
+      </c>
+      <c r="F104" t="s" s="10">
+        <v>11</v>
+      </c>
+      <c r="G104" t="s" s="11">
+        <v>188</v>
+      </c>
+      <c r="H104" t="s" s="11">
+        <v>189</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/Java_Deprecation_Report.xlsx
+++ b/Java_Deprecation_Report.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="193">
   <si>
     <t>Type</t>
   </si>
@@ -605,10 +605,19 @@
     <t>deprecatedProperty</t>
   </si>
   <si>
+    <t>7.0</t>
+  </si>
+  <si>
+    <t>2026-09-13</t>
+  </si>
+  <si>
     <t>MyPojoRequest</t>
   </si>
   <si>
     <t>formerMandatoryRequestProperty</t>
+  </si>
+  <si>
+    <t>MyContext</t>
   </si>
 </sst>
 </file>
@@ -1115,7 +1124,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E1136C3-A1B3-DD42-A00A-DCFCD8D149EA}">
-  <dimension ref="A1:H103"/>
+  <dimension ref="A1:H104"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="9" width="31.5"/>
@@ -3772,36 +3781,62 @@
         <v>11</v>
       </c>
       <c r="G102" t="s" s="11">
-        <v>11</v>
+        <v>188</v>
       </c>
       <c r="H102" t="s" s="11">
-        <v>11</v>
+        <v>189</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="9">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B103" t="s" s="9">
         <v>186</v>
       </c>
       <c r="C103" t="s" s="9">
+        <v>191</v>
+      </c>
+      <c r="D103" t="s" s="9">
+        <v>11</v>
+      </c>
+      <c r="E103" t="s" s="9">
+        <v>11</v>
+      </c>
+      <c r="F103" t="s" s="10">
+        <v>11</v>
+      </c>
+      <c r="G103" t="s" s="11">
+        <v>188</v>
+      </c>
+      <c r="H103" t="s" s="11">
         <v>189</v>
       </c>
-      <c r="D103" t="s" s="9">
-        <v>11</v>
-      </c>
-      <c r="E103" t="s" s="9">
-        <v>11</v>
-      </c>
-      <c r="F103" t="s" s="10">
-        <v>11</v>
-      </c>
-      <c r="G103" t="s" s="11">
-        <v>11</v>
-      </c>
-      <c r="H103" t="s" s="11">
-        <v>11</v>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="9">
+        <v>192</v>
+      </c>
+      <c r="B104" t="s" s="9">
+        <v>186</v>
+      </c>
+      <c r="C104" t="s" s="9">
+        <v>63</v>
+      </c>
+      <c r="D104" t="s" s="9">
+        <v>63</v>
+      </c>
+      <c r="E104" t="s" s="9">
+        <v>11</v>
+      </c>
+      <c r="F104" t="s" s="10">
+        <v>11</v>
+      </c>
+      <c r="G104" t="s" s="11">
+        <v>188</v>
+      </c>
+      <c r="H104" t="s" s="11">
+        <v>189</v>
       </c>
     </row>
   </sheetData>

--- a/Java_Deprecation_Report.xlsx
+++ b/Java_Deprecation_Report.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="203">
   <si>
     <t>Type</t>
   </si>
@@ -617,7 +617,37 @@
     <t>formerMandatoryRequestProperty</t>
   </si>
   <si>
+    <t>MultiVersioningTestService</t>
+  </si>
+  <si>
+    <t>deprecatedEndpoint</t>
+  </si>
+  <si>
+    <t>I'm so deprecated.</t>
+  </si>
+  <si>
     <t>MyContext</t>
+  </si>
+  <si>
+    <t>ClientType</t>
+  </si>
+  <si>
+    <t>CLIENT_3</t>
+  </si>
+  <si>
+    <t>DeprecatedClass</t>
+  </si>
+  <si>
+    <t>DeprecatedOpenAPIDataType</t>
+  </si>
+  <si>
+    <t>AnotherDeprecatedRESTService</t>
+  </si>
+  <si>
+    <t>operationOfADeprecatedService</t>
+  </si>
+  <si>
+    <t>DeprecatedOpenAPIEnum</t>
   </si>
 </sst>
 </file>
@@ -1124,7 +1154,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E1136C3-A1B3-DD42-A00A-DCFCD8D149EA}">
-  <dimension ref="A1:H104"/>
+  <dimension ref="A1:H111"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="9" width="31.5"/>
@@ -3821,13 +3851,13 @@
         <v>186</v>
       </c>
       <c r="C104" t="s" s="9">
-        <v>63</v>
+        <v>193</v>
       </c>
       <c r="D104" t="s" s="9">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="E104" t="s" s="9">
-        <v>11</v>
+        <v>194</v>
       </c>
       <c r="F104" t="s" s="10">
         <v>11</v>
@@ -3836,6 +3866,188 @@
         <v>188</v>
       </c>
       <c r="H104" t="s" s="11">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="9">
+        <v>195</v>
+      </c>
+      <c r="B105" t="s" s="9">
+        <v>186</v>
+      </c>
+      <c r="C105" t="s" s="9">
+        <v>63</v>
+      </c>
+      <c r="D105" t="s" s="9">
+        <v>63</v>
+      </c>
+      <c r="E105" t="s" s="9">
+        <v>11</v>
+      </c>
+      <c r="F105" t="s" s="10">
+        <v>11</v>
+      </c>
+      <c r="G105" t="s" s="11">
+        <v>188</v>
+      </c>
+      <c r="H105" t="s" s="11">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="9">
+        <v>196</v>
+      </c>
+      <c r="B106" t="s" s="9">
+        <v>186</v>
+      </c>
+      <c r="C106" t="s" s="9">
+        <v>197</v>
+      </c>
+      <c r="D106" t="s" s="9">
+        <v>11</v>
+      </c>
+      <c r="E106" t="s" s="9">
+        <v>11</v>
+      </c>
+      <c r="F106" t="s" s="10">
+        <v>11</v>
+      </c>
+      <c r="G106" t="s" s="11">
+        <v>188</v>
+      </c>
+      <c r="H106" t="s" s="11">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="9">
+        <v>198</v>
+      </c>
+      <c r="B107" t="s" s="9">
+        <v>186</v>
+      </c>
+      <c r="C107" t="s" s="9">
+        <v>11</v>
+      </c>
+      <c r="D107" t="s" s="9">
+        <v>11</v>
+      </c>
+      <c r="E107" t="s" s="9">
+        <v>11</v>
+      </c>
+      <c r="F107" t="s" s="10">
+        <v>11</v>
+      </c>
+      <c r="G107" t="s" s="11">
+        <v>188</v>
+      </c>
+      <c r="H107" t="s" s="11">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="9">
+        <v>199</v>
+      </c>
+      <c r="B108" t="s" s="9">
+        <v>186</v>
+      </c>
+      <c r="C108" t="s" s="9">
+        <v>11</v>
+      </c>
+      <c r="D108" t="s" s="9">
+        <v>11</v>
+      </c>
+      <c r="E108" t="s" s="9">
+        <v>11</v>
+      </c>
+      <c r="F108" t="s" s="10">
+        <v>11</v>
+      </c>
+      <c r="G108" t="s" s="11">
+        <v>188</v>
+      </c>
+      <c r="H108" t="s" s="11">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="9">
+        <v>200</v>
+      </c>
+      <c r="B109" t="s" s="9">
+        <v>186</v>
+      </c>
+      <c r="C109" t="s" s="9">
+        <v>11</v>
+      </c>
+      <c r="D109" t="s" s="9">
+        <v>11</v>
+      </c>
+      <c r="E109" t="s" s="9">
+        <v>11</v>
+      </c>
+      <c r="F109" t="s" s="10">
+        <v>11</v>
+      </c>
+      <c r="G109" t="s" s="11">
+        <v>188</v>
+      </c>
+      <c r="H109" t="s" s="11">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="9">
+        <v>200</v>
+      </c>
+      <c r="B110" t="s" s="9">
+        <v>186</v>
+      </c>
+      <c r="C110" t="s" s="9">
+        <v>201</v>
+      </c>
+      <c r="D110" t="s" s="9">
+        <v>11</v>
+      </c>
+      <c r="E110" t="s" s="9">
+        <v>11</v>
+      </c>
+      <c r="F110" t="s" s="10">
+        <v>11</v>
+      </c>
+      <c r="G110" t="s" s="11">
+        <v>188</v>
+      </c>
+      <c r="H110" t="s" s="11">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="9">
+        <v>202</v>
+      </c>
+      <c r="B111" t="s" s="9">
+        <v>186</v>
+      </c>
+      <c r="C111" t="s" s="9">
+        <v>202</v>
+      </c>
+      <c r="D111" t="s" s="9">
+        <v>11</v>
+      </c>
+      <c r="E111" t="s" s="9">
+        <v>11</v>
+      </c>
+      <c r="F111" t="s" s="10">
+        <v>11</v>
+      </c>
+      <c r="G111" t="s" s="11">
+        <v>188</v>
+      </c>
+      <c r="H111" t="s" s="11">
         <v>189</v>
       </c>
     </row>

--- a/Java_Deprecation_Report.xlsx
+++ b/Java_Deprecation_Report.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tillmann.schall/Projects/JEAF/jeaf-generator/jeaf-generator/src/main/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EC330ED-BB34-4043-A273-9B77F23749F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{940AF31E-6AD2-F249-98B2-260B852C4C26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36860" yWindow="2360" windowWidth="51160" windowHeight="28140" xr2:uid="{441949ED-3404-8548-92CD-A40A7EA6D1DC}"/>
+    <workbookView xWindow="36860" yWindow="660" windowWidth="51160" windowHeight="28140" xr2:uid="{441949ED-3404-8548-92CD-A40A7EA6D1DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,9 +41,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="203">
   <si>
-    <t>Type</t>
-  </si>
-  <si>
     <t>Package</t>
   </si>
   <si>
@@ -63,6 +60,9 @@
   </si>
   <si>
     <t>Removal Date</t>
+  </si>
+  <si>
+    <t>Element</t>
   </si>
   <si>
     <t>EnumWithDeprecatedProperty</t>
@@ -730,25 +730,25 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -783,12 +783,6 @@
       <alignment vertical="top" textRotation="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment vertical="top" textRotation="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
@@ -801,11 +795,17 @@
       </border>
     </dxf>
     <dxf>
+      <alignment vertical="top" textRotation="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <border outline="0">
         <bottom style="thin">
           <color theme="4"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -821,13 +821,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5FC88E85-2BB1-CD48-A0D0-BB78642BF973}" name="Table1" displayName="Table1" ref="A1:H1048576" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4" headerRowBorderDxfId="11" tableBorderDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5FC88E85-2BB1-CD48-A0D0-BB78642BF973}" name="Table1" displayName="Table1" ref="A1:H1048576" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8">
   <autoFilter ref="A1:H1048576" xr:uid="{5FC88E85-2BB1-CD48-A0D0-BB78642BF973}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{A4DDCCBB-E133-DF45-8389-C4AD19D8AEB7}" name="Type" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{439690A4-77A7-D848-A33C-19AF8EF0CF49}" name="Package" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{BC971382-1AD8-4C4D-972D-DF92F8F0260A}" name="Property / Operation" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{5A67E0BD-2295-9F48-B6C2-59EBC6AF29B1}" name="HTTP Header" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{A4DDCCBB-E133-DF45-8389-C4AD19D8AEB7}" name="Element" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{439690A4-77A7-D848-A33C-19AF8EF0CF49}" name="Package" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{BC971382-1AD8-4C4D-972D-DF92F8F0260A}" name="Property / Operation" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{5A67E0BD-2295-9F48-B6C2-59EBC6AF29B1}" name="HTTP Header" dataDxfId="4"/>
     <tableColumn id="5" xr3:uid="{1DDDD3D3-BC66-DB4E-A899-65EA0DA59605}" name="Description" dataDxfId="3"/>
     <tableColumn id="6" xr3:uid="{122F67FD-2569-C44A-A432-EAFF5935108B}" name="Deprecated since" dataDxfId="2"/>
     <tableColumn id="7" xr3:uid="{4B86B03A-67C7-E347-8943-3AB848258236}" name="Planned to be removed" dataDxfId="1"/>
@@ -1167,28 +1167,28 @@
   <sheetData>
     <row r="1" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>6</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2">

--- a/Java_Deprecation_Report.xlsx
+++ b/Java_Deprecation_Report.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="208">
   <si>
     <t>Package</t>
   </si>
@@ -101,7 +101,7 @@
     <t>pParam2</t>
   </si>
   <si>
-    <t>JEAFTestService</t>
+    <t>JEAFTestService.checkRequiredService_2(...)</t>
   </si>
   <si>
     <t>com.anaptecs.jeaf.junit.core</t>
@@ -110,7 +110,7 @@
     <t>checkRequiredService_2</t>
   </si>
   <si>
-    <t>BusinessObjectTestService</t>
+    <t>BusinessObjectTestService.deprectedOperation(...)</t>
   </si>
   <si>
     <t>deprectedOperation</t>
@@ -137,6 +137,9 @@
     <t>deprecatedRefs</t>
   </si>
   <si>
+    <t>PartiallyDeprecatedServiceObject.doSomethingDeprecated(...)</t>
+  </si>
+  <si>
     <t>doSomethingDeprecated</t>
   </si>
   <si>
@@ -191,7 +194,7 @@
     <t>2023-12-31</t>
   </si>
   <si>
-    <t>ServiceWithDeprecations</t>
+    <t>ServiceWithDeprecations.createSomething(...)</t>
   </si>
   <si>
     <t>createSomething</t>
@@ -296,6 +299,9 @@
     <t>verbindungspunkte</t>
   </si>
   <si>
+    <t>Price.recalculatePrice(...)</t>
+  </si>
+  <si>
     <t>recalculatePrice</t>
   </si>
   <si>
@@ -329,6 +335,9 @@
     <t>baseClasses</t>
   </si>
   <si>
+    <t>DeprecatedPO.doSomethingDeprecated(...)</t>
+  </si>
+  <si>
     <t>PersistenceTest</t>
   </si>
   <si>
@@ -476,7 +485,7 @@
     <t>99.9</t>
   </si>
   <si>
-    <t>ProductService</t>
+    <t>ProductService.deprecatedOperation(...)</t>
   </si>
   <si>
     <t>com.anaptecs.jeaf.junit.openapi.service1</t>
@@ -518,7 +527,7 @@
     <t>deprecatedComplexReturn</t>
   </si>
   <si>
-    <t>PlainPOJO</t>
+    <t>PlainPOJO.doDeprectedStuff(...)</t>
   </si>
   <si>
     <t>com.anaptecs.jeaf.junit.pojo</t>
@@ -551,7 +560,7 @@
     <t>BChildPOJO</t>
   </si>
   <si>
-    <t>RESTTestService</t>
+    <t>RESTTestService.deprecatedOperation(...)</t>
   </si>
   <si>
     <t>com.anaptecs.jeaf.junit.rest</t>
@@ -575,13 +584,16 @@
     <t>deprecatedAsyncParam</t>
   </si>
   <si>
+    <t>RESTTestService.deprecatedAsync(...)</t>
+  </si>
+  <si>
     <t>deprecatedAsync</t>
   </si>
   <si>
     <t>DeprecatedRESTService</t>
   </si>
   <si>
-    <t>MyServiceProvider</t>
+    <t>MyServiceProvider.doSomethingDeprecated(...)</t>
   </si>
   <si>
     <t>com.anaptecs.jeaf.junit.serviceproviders</t>
@@ -617,7 +629,7 @@
     <t>formerMandatoryRequestProperty</t>
   </si>
   <si>
-    <t>MultiVersioningTestService</t>
+    <t>MultiVersioningTestService.deprecatedEndpoint(...)</t>
   </si>
   <si>
     <t>deprecatedEndpoint</t>
@@ -642,6 +654,9 @@
   </si>
   <si>
     <t>AnotherDeprecatedRESTService</t>
+  </si>
+  <si>
+    <t>AnotherDeprecatedRESTService.operationOfADeprecatedService(...)</t>
   </si>
   <si>
     <t>operationOfADeprecatedService</t>
@@ -1505,13 +1520,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="9">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B14" t="s" s="9">
         <v>21</v>
       </c>
       <c r="C14" t="s" s="9">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D14" t="s" s="9">
         <v>11</v>
@@ -1531,7 +1546,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="9">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s" s="9">
         <v>21</v>
@@ -1557,7 +1572,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="9">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B16" t="s" s="9">
         <v>21</v>
@@ -1583,7 +1598,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="9">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B17" t="s" s="9">
         <v>21</v>
@@ -1609,7 +1624,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="9">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B18" t="s" s="9">
         <v>21</v>
@@ -1635,13 +1650,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="9">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B19" t="s" s="9">
         <v>21</v>
       </c>
       <c r="C19" t="s" s="9">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D19" t="s" s="9">
         <v>11</v>
@@ -1661,7 +1676,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="9">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B20" t="s" s="9">
         <v>21</v>
@@ -1687,13 +1702,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="9">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B21" t="s" s="9">
         <v>21</v>
       </c>
       <c r="C21" t="s" s="9">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D21" t="s" s="9">
         <v>11</v>
@@ -1713,19 +1728,19 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="9">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B22" t="s" s="9">
         <v>21</v>
       </c>
       <c r="C22" t="s" s="9">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D22" t="s" s="9">
         <v>11</v>
       </c>
       <c r="E22" t="s" s="9">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F22" t="s" s="10">
         <v>11</v>
@@ -1739,7 +1754,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="9">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B23" t="s" s="9">
         <v>21</v>
@@ -1765,7 +1780,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="9">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B24" t="s" s="9">
         <v>21</v>
@@ -1791,10 +1806,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="9">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B25" t="s" s="9">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C25" t="s" s="9">
         <v>11</v>
@@ -1803,13 +1818,13 @@
         <v>11</v>
       </c>
       <c r="E25" t="s" s="9">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F25" t="s" s="10">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G25" t="s" s="11">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H25" t="s" s="11">
         <v>11</v>
@@ -1817,25 +1832,25 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="9">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B26" t="s" s="9">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C26" t="s" s="9">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D26" t="s" s="9">
         <v>11</v>
       </c>
       <c r="E26" t="s" s="9">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F26" t="s" s="10">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G26" t="s" s="11">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H26" t="s" s="11">
         <v>11</v>
@@ -1843,19 +1858,19 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="9">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B27" t="s" s="9">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C27" t="s" s="9">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D27" t="s" s="9">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E27" t="s" s="9">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F27" t="s" s="10">
         <v>11</v>
@@ -1869,13 +1884,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="9">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B28" t="s" s="9">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C28" t="s" s="9">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D28" t="s" s="9">
         <v>11</v>
@@ -1895,19 +1910,19 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="9">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B29" t="s" s="9">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C29" t="s" s="9">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D29" t="s" s="9">
         <v>11</v>
       </c>
       <c r="E29" t="s" s="9">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F29" t="s" s="10">
         <v>11</v>
@@ -1921,25 +1936,25 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="9">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B30" t="s" s="9">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C30" t="s" s="9">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D30" t="s" s="9">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E30" t="s" s="9">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F30" t="s" s="10">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G30" t="s" s="11">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H30" t="s" s="11">
         <v>11</v>
@@ -1947,25 +1962,25 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="9">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B31" t="s" s="9">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C31" t="s" s="9">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D31" t="s" s="9">
         <v>11</v>
       </c>
       <c r="E31" t="s" s="9">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F31" t="s" s="10">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G31" t="s" s="11">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H31" t="s" s="11">
         <v>11</v>
@@ -1973,10 +1988,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="9">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B32" t="s" s="9">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C32" t="s" s="9">
         <v>11</v>
@@ -1985,7 +2000,7 @@
         <v>11</v>
       </c>
       <c r="E32" t="s" s="9">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F32" t="s" s="10">
         <v>11</v>
@@ -1999,10 +2014,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="9">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B33" t="s" s="9">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C33" t="s" s="9">
         <v>11</v>
@@ -2025,13 +2040,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="9">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B34" t="s" s="9">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C34" t="s" s="9">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D34" t="s" s="9">
         <v>11</v>
@@ -2051,25 +2066,25 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="9">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B35" t="s" s="9">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C35" t="s" s="9">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D35" t="s" s="9">
         <v>11</v>
       </c>
       <c r="E35" t="s" s="9">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F35" t="s" s="10">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G35" t="s" s="11">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s" s="11">
         <v>11</v>
@@ -2077,10 +2092,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="9">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B36" t="s" s="9">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C36" t="s" s="9">
         <v>11</v>
@@ -2103,13 +2118,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="9">
+        <v>82</v>
+      </c>
+      <c r="B37" t="s" s="9">
         <v>81</v>
       </c>
-      <c r="B37" t="s" s="9">
-        <v>80</v>
-      </c>
       <c r="C37" t="s" s="9">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D37" t="s" s="9">
         <v>11</v>
@@ -2129,13 +2144,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="9">
+        <v>82</v>
+      </c>
+      <c r="B38" t="s" s="9">
         <v>81</v>
       </c>
-      <c r="B38" t="s" s="9">
-        <v>80</v>
-      </c>
       <c r="C38" t="s" s="9">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D38" t="s" s="9">
         <v>11</v>
@@ -2155,13 +2170,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="9">
+        <v>82</v>
+      </c>
+      <c r="B39" t="s" s="9">
         <v>81</v>
       </c>
-      <c r="B39" t="s" s="9">
-        <v>80</v>
-      </c>
       <c r="C39" t="s" s="9">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D39" t="s" s="9">
         <v>11</v>
@@ -2181,13 +2196,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="9">
+        <v>86</v>
+      </c>
+      <c r="B40" t="s" s="9">
         <v>81</v>
       </c>
-      <c r="B40" t="s" s="9">
-        <v>80</v>
-      </c>
       <c r="C40" t="s" s="9">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D40" t="s" s="9">
         <v>11</v>
@@ -2207,10 +2222,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="9">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B41" t="s" s="9">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C41" t="s" s="9">
         <v>19</v>
@@ -2233,10 +2248,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="9">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B42" t="s" s="9">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C42" t="s" s="9">
         <v>11</v>
@@ -2259,10 +2274,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="9">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B43" t="s" s="9">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C43" t="s" s="9">
         <v>11</v>
@@ -2285,13 +2300,13 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="9">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B44" t="s" s="9">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C44" t="s" s="9">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D44" t="s" s="9">
         <v>11</v>
@@ -2311,10 +2326,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="9">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B45" t="s" s="9">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C45" t="s" s="9">
         <v>11</v>
@@ -2337,13 +2352,13 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="9">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B46" t="s" s="9">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C46" t="s" s="9">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D46" t="s" s="9">
         <v>11</v>
@@ -2363,13 +2378,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="9">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B47" t="s" s="9">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C47" t="s" s="9">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D47" t="s" s="9">
         <v>11</v>
@@ -2389,13 +2404,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="9">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B48" t="s" s="9">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C48" t="s" s="9">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D48" t="s" s="9">
         <v>11</v>
@@ -2415,13 +2430,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="9">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B49" t="s" s="9">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C49" t="s" s="9">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D49" t="s" s="9">
         <v>11</v>
@@ -2441,10 +2456,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="9">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B50" t="s" s="9">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C50" t="s" s="9">
         <v>19</v>
@@ -2467,10 +2482,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="9">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B51" t="s" s="9">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C51" t="s" s="9">
         <v>11</v>
@@ -2493,13 +2508,13 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="9">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B52" t="s" s="9">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C52" t="s" s="9">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D52" t="s" s="9">
         <v>11</v>
@@ -2519,13 +2534,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="9">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B53" t="s" s="9">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C53" t="s" s="9">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D53" t="s" s="9">
         <v>11</v>
@@ -2545,19 +2560,19 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="9">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B54" t="s" s="9">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C54" t="s" s="9">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D54" t="s" s="9">
         <v>11</v>
       </c>
       <c r="E54" t="s" s="9">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F54" t="s" s="10">
         <v>11</v>
@@ -2571,13 +2586,13 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="9">
+        <v>107</v>
+      </c>
+      <c r="B55" t="s" s="9">
         <v>104</v>
       </c>
-      <c r="B55" t="s" s="9">
-        <v>101</v>
-      </c>
       <c r="C55" t="s" s="9">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D55" t="s" s="9">
         <v>11</v>
@@ -2597,13 +2612,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="9">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B56" t="s" s="9">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C56" t="s" s="9">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D56" t="s" s="9">
         <v>11</v>
@@ -2623,13 +2638,13 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="9">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B57" t="s" s="9">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C57" t="s" s="9">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D57" t="s" s="9">
         <v>11</v>
@@ -2649,10 +2664,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="9">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B58" t="s" s="9">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C58" t="s" s="9">
         <v>11</v>
@@ -2661,13 +2676,13 @@
         <v>11</v>
       </c>
       <c r="E58" t="s" s="9">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F58" t="s" s="10">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G58" t="s" s="11">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H58" t="s" s="11">
         <v>11</v>
@@ -2675,19 +2690,19 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="9">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B59" t="s" s="9">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C59" t="s" s="9">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D59" t="s" s="9">
         <v>11</v>
       </c>
       <c r="E59" t="s" s="9">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F59" t="s" s="10">
         <v>11</v>
@@ -2701,13 +2716,13 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="9">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B60" t="s" s="9">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C60" t="s" s="9">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D60" t="s" s="9">
         <v>11</v>
@@ -2727,13 +2742,13 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="9">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B61" t="s" s="9">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C61" t="s" s="9">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D61" t="s" s="9">
         <v>11</v>
@@ -2753,13 +2768,13 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="9">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B62" t="s" s="9">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C62" t="s" s="9">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D62" t="s" s="9">
         <v>11</v>
@@ -2779,13 +2794,13 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="9">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B63" t="s" s="9">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C63" t="s" s="9">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D63" t="s" s="9">
         <v>11</v>
@@ -2805,10 +2820,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="9">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B64" t="s" s="9">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C64" t="s" s="9">
         <v>11</v>
@@ -2823,7 +2838,7 @@
         <v>11</v>
       </c>
       <c r="G64" t="s" s="11">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H64" t="s" s="11">
         <v>11</v>
@@ -2831,19 +2846,19 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="9">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B65" t="s" s="9">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C65" t="s" s="9">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D65" t="s" s="9">
         <v>11</v>
       </c>
       <c r="E65" t="s" s="9">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F65" t="s" s="10">
         <v>11</v>
@@ -2857,16 +2872,16 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="9">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B66" t="s" s="9">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C66" t="s" s="9">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D66" t="s" s="9">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E66" t="s" s="9">
         <v>11</v>
@@ -2875,7 +2890,7 @@
         <v>11</v>
       </c>
       <c r="G66" t="s" s="11">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H66" t="s" s="11">
         <v>11</v>
@@ -2883,13 +2898,13 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="9">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B67" t="s" s="9">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C67" t="s" s="9">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D67" t="s" s="9">
         <v>11</v>
@@ -2909,13 +2924,13 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="9">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B68" t="s" s="9">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C68" t="s" s="9">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D68" t="s" s="9">
         <v>11</v>
@@ -2935,13 +2950,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="9">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B69" t="s" s="9">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C69" t="s" s="9">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D69" t="s" s="9">
         <v>11</v>
@@ -2961,13 +2976,13 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="9">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B70" t="s" s="9">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C70" t="s" s="9">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D70" t="s" s="9">
         <v>11</v>
@@ -2987,25 +3002,25 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="9">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B71" t="s" s="9">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C71" t="s" s="9">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D71" t="s" s="9">
         <v>11</v>
       </c>
       <c r="E71" t="s" s="9">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F71" t="s" s="10">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G71" t="s" s="11">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="H71" t="s" s="11">
         <v>11</v>
@@ -3013,25 +3028,25 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="9">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B72" t="s" s="9">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C72" t="s" s="9">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D72" t="s" s="9">
         <v>11</v>
       </c>
       <c r="E72" t="s" s="9">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F72" t="s" s="10">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G72" t="s" s="11">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="H72" t="s" s="11">
         <v>11</v>
@@ -3039,13 +3054,13 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="9">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B73" t="s" s="9">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C73" t="s" s="9">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D73" t="s" s="9">
         <v>11</v>
@@ -3065,25 +3080,25 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="9">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B74" t="s" s="9">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C74" t="s" s="9">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D74" t="s" s="9">
         <v>11</v>
       </c>
       <c r="E74" t="s" s="9">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F74" t="s" s="10">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="G74" t="s" s="11">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="H74" t="s" s="11">
         <v>11</v>
@@ -3091,10 +3106,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="9">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B75" t="s" s="9">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C75" t="s" s="9">
         <v>11</v>
@@ -3117,25 +3132,25 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="9">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B76" t="s" s="9">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C76" t="s" s="9">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D76" t="s" s="9">
         <v>11</v>
       </c>
       <c r="E76" t="s" s="9">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F76" t="s" s="10">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G76" t="s" s="11">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="H76" t="s" s="11">
         <v>11</v>
@@ -3143,16 +3158,16 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="9">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B77" t="s" s="9">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C77" t="s" s="9">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D77" t="s" s="9">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E77" t="s" s="9">
         <v>11</v>
@@ -3169,10 +3184,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="9">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B78" t="s" s="9">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C78" t="s" s="9">
         <v>11</v>
@@ -3195,13 +3210,13 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="9">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B79" t="s" s="9">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C79" t="s" s="9">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D79" t="s" s="9">
         <v>11</v>
@@ -3221,13 +3236,13 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="9">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B80" t="s" s="9">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C80" t="s" s="9">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D80" t="s" s="9">
         <v>11</v>
@@ -3247,10 +3262,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="9">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B81" t="s" s="9">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C81" t="s" s="9">
         <v>11</v>
@@ -3273,13 +3288,13 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="9">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B82" t="s" s="9">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C82" t="s" s="9">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D82" t="s" s="9">
         <v>11</v>
@@ -3299,13 +3314,13 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="9">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B83" t="s" s="9">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C83" t="s" s="9">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D83" t="s" s="9">
         <v>11</v>
@@ -3325,10 +3340,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="9">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B84" t="s" s="9">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C84" t="s" s="9">
         <v>11</v>
@@ -3351,13 +3366,13 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="9">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B85" t="s" s="9">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C85" t="s" s="9">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D85" t="s" s="9">
         <v>11</v>
@@ -3377,10 +3392,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="9">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B86" t="s" s="9">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C86" t="s" s="9">
         <v>11</v>
@@ -3389,13 +3404,13 @@
         <v>11</v>
       </c>
       <c r="E86" t="s" s="9">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F86" t="s" s="10">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="G86" t="s" s="11">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="H86" t="s" s="11">
         <v>11</v>
@@ -3403,10 +3418,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="9">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B87" t="s" s="9">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C87" t="s" s="9">
         <v>31</v>
@@ -3429,10 +3444,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="9">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B88" t="s" s="9">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C88" t="s" s="9">
         <v>11</v>
@@ -3455,25 +3470,25 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="9">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B89" t="s" s="9">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C89" t="s" s="9">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D89" t="s" s="9">
         <v>11</v>
       </c>
       <c r="E89" t="s" s="9">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F89" t="s" s="10">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G89" t="s" s="11">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H89" t="s" s="11">
         <v>11</v>
@@ -3481,10 +3496,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="9">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B90" t="s" s="9">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C90" t="s" s="9">
         <v>19</v>
@@ -3507,10 +3522,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="9">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B91" t="s" s="9">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C91" t="s" s="9">
         <v>11</v>
@@ -3533,13 +3548,13 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="9">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B92" t="s" s="9">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C92" t="s" s="9">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D92" t="s" s="9">
         <v>11</v>
@@ -3559,10 +3574,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="9">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B93" t="s" s="9">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C93" t="s" s="9">
         <v>11</v>
@@ -3585,13 +3600,13 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="9">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="B94" t="s" s="9">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C94" t="s" s="9">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D94" t="s" s="9">
         <v>11</v>
@@ -3611,10 +3626,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="9">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B95" t="s" s="9">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C95" t="s" s="9">
         <v>11</v>
@@ -3637,13 +3652,13 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="9">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B96" t="s" s="9">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C96" t="s" s="9">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D96" t="s" s="9">
         <v>11</v>
@@ -3663,10 +3678,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="9">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B97" t="s" s="9">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C97" t="s" s="9">
         <v>19</v>
@@ -3689,10 +3704,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="9">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B98" t="s" s="9">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C98" t="s" s="9">
         <v>11</v>
@@ -3715,13 +3730,13 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="9">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B99" t="s" s="9">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C99" t="s" s="9">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D99" t="s" s="9">
         <v>11</v>
@@ -3741,10 +3756,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="9">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B100" t="s" s="9">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C100" t="s" s="9">
         <v>11</v>
@@ -3767,10 +3782,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="9">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B101" t="s" s="9">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C101" t="s" s="9">
         <v>11</v>
@@ -3793,13 +3808,13 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="9">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B102" t="s" s="9">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C102" t="s" s="9">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D102" t="s" s="9">
         <v>11</v>
@@ -3811,21 +3826,21 @@
         <v>11</v>
       </c>
       <c r="G102" t="s" s="11">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="H102" t="s" s="11">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="9">
+        <v>194</v>
+      </c>
+      <c r="B103" t="s" s="9">
         <v>190</v>
       </c>
-      <c r="B103" t="s" s="9">
-        <v>186</v>
-      </c>
       <c r="C103" t="s" s="9">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D103" t="s" s="9">
         <v>11</v>
@@ -3837,50 +3852,50 @@
         <v>11</v>
       </c>
       <c r="G103" t="s" s="11">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="H103" t="s" s="11">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="9">
+        <v>196</v>
+      </c>
+      <c r="B104" t="s" s="9">
+        <v>190</v>
+      </c>
+      <c r="C104" t="s" s="9">
+        <v>197</v>
+      </c>
+      <c r="D104" t="s" s="9">
+        <v>11</v>
+      </c>
+      <c r="E104" t="s" s="9">
+        <v>198</v>
+      </c>
+      <c r="F104" t="s" s="10">
+        <v>11</v>
+      </c>
+      <c r="G104" t="s" s="11">
         <v>192</v>
       </c>
-      <c r="B104" t="s" s="9">
-        <v>186</v>
-      </c>
-      <c r="C104" t="s" s="9">
+      <c r="H104" t="s" s="11">
         <v>193</v>
-      </c>
-      <c r="D104" t="s" s="9">
-        <v>11</v>
-      </c>
-      <c r="E104" t="s" s="9">
-        <v>194</v>
-      </c>
-      <c r="F104" t="s" s="10">
-        <v>11</v>
-      </c>
-      <c r="G104" t="s" s="11">
-        <v>188</v>
-      </c>
-      <c r="H104" t="s" s="11">
-        <v>189</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="9">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B105" t="s" s="9">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C105" t="s" s="9">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D105" t="s" s="9">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E105" t="s" s="9">
         <v>11</v>
@@ -3889,21 +3904,21 @@
         <v>11</v>
       </c>
       <c r="G105" t="s" s="11">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="H105" t="s" s="11">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="9">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B106" t="s" s="9">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C106" t="s" s="9">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="D106" t="s" s="9">
         <v>11</v>
@@ -3915,18 +3930,18 @@
         <v>11</v>
       </c>
       <c r="G106" t="s" s="11">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="H106" t="s" s="11">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="9">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B107" t="s" s="9">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C107" t="s" s="9">
         <v>11</v>
@@ -3941,18 +3956,18 @@
         <v>11</v>
       </c>
       <c r="G107" t="s" s="11">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="H107" t="s" s="11">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="9">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B108" t="s" s="9">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C108" t="s" s="9">
         <v>11</v>
@@ -3967,18 +3982,18 @@
         <v>11</v>
       </c>
       <c r="G108" t="s" s="11">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="H108" t="s" s="11">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="9">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B109" t="s" s="9">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C109" t="s" s="9">
         <v>11</v>
@@ -3993,21 +4008,21 @@
         <v>11</v>
       </c>
       <c r="G109" t="s" s="11">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="H109" t="s" s="11">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="9">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B110" t="s" s="9">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C110" t="s" s="9">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="D110" t="s" s="9">
         <v>11</v>
@@ -4019,21 +4034,21 @@
         <v>11</v>
       </c>
       <c r="G110" t="s" s="11">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="H110" t="s" s="11">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="9">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B111" t="s" s="9">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C111" t="s" s="9">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="D111" t="s" s="9">
         <v>11</v>
@@ -4045,10 +4060,10 @@
         <v>11</v>
       </c>
       <c r="G111" t="s" s="11">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="H111" t="s" s="11">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
